--- a/docs/design/02_画面設計書_HackerLake.xlsx
+++ b/docs/design/02_画面設計書_HackerLake.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phrx4\hackerlake\docs\design\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{557CD990-DC3B-4DBD-84A1-AEDD63FCBED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F1AD9080-9C21-4EEE-AB94-0EDCD5C6DD0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{A8652AA7-4506-4EF0-B54B-6724164B11B4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{4FB0A5AB-296D-4FB0-9741-B827CFE824D7}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,20 @@
     <sheet name="状態遷移" sheetId="5" r:id="rId5"/>
     <sheet name="アクセシビリティ" sheetId="6" r:id="rId6"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">アクセシビリティ!$A$3:$H$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">アニメーション仕様!$A$3:$H$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">レイアウト!$A$3:$H$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">画面一覧!$A$3:$H$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">状態遷移!$A$3:$H$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">表紙!$A$3:$H$6</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">アクセシビリティ!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">アニメーション仕様!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">レイアウト!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">画面一覧!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">状態遷移!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">表紙!$1:$3</definedName>
+  </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -681,7 +695,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -708,15 +722,21 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FFFFFFFF"/>
-      <name val="游ゴシック"/>
+      <name val="Yu Gothic"/>
       <family val="3"/>
       <charset val="128"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -732,6 +752,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF006080"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7FAFC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -765,7 +791,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -773,12 +799,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1094,18 +1123,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E075E90C-8E75-46B1-BFA6-EF3584653422}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{953E2EFA-7AAF-484C-8523-E87D7C4B18B9}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="16.625" customWidth="1"/>
-    <col min="2" max="2" width="24.625" customWidth="1"/>
-    <col min="3" max="3" width="34.625" customWidth="1"/>
-    <col min="4" max="5" width="42.625" customWidth="1"/>
-    <col min="6" max="8" width="28.625" customWidth="1"/>
+    <col min="1" max="1" width="15.625" customWidth="1"/>
+    <col min="2" max="2" width="22.625" customWidth="1"/>
+    <col min="3" max="3" width="36.625" customWidth="1"/>
+    <col min="4" max="5" width="46.625" customWidth="1"/>
+    <col min="6" max="7" width="28.625" customWidth="1"/>
+    <col min="8" max="8" width="24.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" ht="27.95" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1117,7 +1150,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
     </row>
-    <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" ht="32.1" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -1143,7 +1176,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
@@ -1161,33 +1194,33 @@
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
     </row>
-    <row r="5" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:8" ht="33.950000000000003" customHeight="1">
+      <c r="A5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="5">
         <v>46186</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>20</v>
       </c>
@@ -1214,27 +1247,33 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A3:H6" xr:uid="{953E2EFA-7AAF-484C-8523-E87D7C4B18B9}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.3" right="0.3" top="0.44999999999999996" bottom="0.44999999999999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="52" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B598CC32-8E80-4E28-BA27-319718EF8DD8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{899281C4-252E-4518-A70B-A7103CFB72D2}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="16.625" customWidth="1"/>
-    <col min="2" max="2" width="24.625" customWidth="1"/>
-    <col min="3" max="3" width="34.625" customWidth="1"/>
-    <col min="4" max="5" width="42.625" customWidth="1"/>
-    <col min="6" max="8" width="28.625" customWidth="1"/>
+    <col min="1" max="1" width="15.625" customWidth="1"/>
+    <col min="2" max="2" width="22.625" customWidth="1"/>
+    <col min="3" max="3" width="36.625" customWidth="1"/>
+    <col min="4" max="5" width="46.625" customWidth="1"/>
+    <col min="6" max="7" width="28.625" customWidth="1"/>
+    <col min="8" max="8" width="24.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" ht="27.95" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
@@ -1246,7 +1285,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
     </row>
-    <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" ht="32.1" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>29</v>
       </c>
@@ -1272,7 +1311,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>37</v>
       </c>
@@ -1298,33 +1337,33 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:8" ht="33.950000000000003" customHeight="1">
+      <c r="A5" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>50</v>
       </c>
@@ -1350,33 +1389,33 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:8" ht="33.950000000000003" customHeight="1">
+      <c r="A7" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="H7" s="4" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A8" s="3" t="s">
         <v>63</v>
       </c>
@@ -1403,27 +1442,33 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A3:H8" xr:uid="{899281C4-252E-4518-A70B-A7103CFB72D2}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.3" right="0.3" top="0.44999999999999996" bottom="0.44999999999999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="52" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4101C51-B6DA-4AC0-9639-1B2ED37F72D8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C8AF87C-AB0D-46B6-86CE-C62E12024C88}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="16.625" customWidth="1"/>
-    <col min="2" max="2" width="24.625" customWidth="1"/>
-    <col min="3" max="3" width="34.625" customWidth="1"/>
-    <col min="4" max="5" width="42.625" customWidth="1"/>
-    <col min="6" max="8" width="28.625" customWidth="1"/>
+    <col min="1" max="1" width="15.625" customWidth="1"/>
+    <col min="2" max="2" width="22.625" customWidth="1"/>
+    <col min="3" max="3" width="36.625" customWidth="1"/>
+    <col min="4" max="5" width="46.625" customWidth="1"/>
+    <col min="6" max="7" width="28.625" customWidth="1"/>
+    <col min="8" max="8" width="24.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" ht="27.95" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>68</v>
       </c>
@@ -1435,7 +1480,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
     </row>
-    <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" ht="32.1" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>69</v>
       </c>
@@ -1461,7 +1506,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>75</v>
       </c>
@@ -1485,31 +1530,31 @@
       </c>
       <c r="H4" s="3"/>
     </row>
-    <row r="5" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:8" ht="33.950000000000003" customHeight="1">
+      <c r="A5" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="H5" s="3"/>
-    </row>
-    <row r="6" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="H5" s="4"/>
+    </row>
+    <row r="6" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>85</v>
       </c>
@@ -1533,31 +1578,31 @@
       </c>
       <c r="H6" s="3"/>
     </row>
-    <row r="7" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:8" ht="33.950000000000003" customHeight="1">
+      <c r="A7" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="H7" s="3"/>
-    </row>
-    <row r="8" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="H7" s="4"/>
+    </row>
+    <row r="8" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A8" s="3" t="s">
         <v>95</v>
       </c>
@@ -1582,27 +1627,33 @@
       <c r="H8" s="3"/>
     </row>
   </sheetData>
+  <autoFilter ref="A3:H8" xr:uid="{5C8AF87C-AB0D-46B6-86CE-C62E12024C88}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.3" right="0.3" top="0.44999999999999996" bottom="0.44999999999999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="52" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A3E7923-23DC-4D85-A8D1-4523E905886B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16B9D37C-54AD-4483-9869-87E825068150}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="16.625" customWidth="1"/>
-    <col min="2" max="2" width="24.625" customWidth="1"/>
-    <col min="3" max="3" width="34.625" customWidth="1"/>
-    <col min="4" max="5" width="42.625" customWidth="1"/>
-    <col min="6" max="8" width="28.625" customWidth="1"/>
+    <col min="1" max="1" width="15.625" customWidth="1"/>
+    <col min="2" max="2" width="22.625" customWidth="1"/>
+    <col min="3" max="3" width="36.625" customWidth="1"/>
+    <col min="4" max="5" width="46.625" customWidth="1"/>
+    <col min="6" max="7" width="28.625" customWidth="1"/>
+    <col min="8" max="8" width="24.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" ht="27.95" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>100</v>
       </c>
@@ -1614,7 +1665,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
     </row>
-    <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" ht="32.1" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>69</v>
       </c>
@@ -1640,7 +1691,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>108</v>
       </c>
@@ -1666,33 +1717,33 @@
         <v>115</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:8" ht="33.950000000000003" customHeight="1">
+      <c r="A5" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="4" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>123</v>
       </c>
@@ -1718,33 +1769,33 @@
         <v>115</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:8" ht="33.950000000000003" customHeight="1">
+      <c r="A7" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="H7" s="4" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A8" s="3" t="s">
         <v>136</v>
       </c>
@@ -1771,27 +1822,33 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A3:H8" xr:uid="{16B9D37C-54AD-4483-9869-87E825068150}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.3" right="0.3" top="0.44999999999999996" bottom="0.44999999999999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="52" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{326731C6-430E-405A-B4BD-C98737A4F2C7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F04D56A7-55FA-49B7-A97D-53AA132D8E63}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:H10"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="16.625" customWidth="1"/>
-    <col min="2" max="2" width="24.625" customWidth="1"/>
-    <col min="3" max="3" width="34.625" customWidth="1"/>
-    <col min="4" max="5" width="42.625" customWidth="1"/>
-    <col min="6" max="8" width="28.625" customWidth="1"/>
+    <col min="1" max="1" width="15.625" customWidth="1"/>
+    <col min="2" max="2" width="22.625" customWidth="1"/>
+    <col min="3" max="3" width="36.625" customWidth="1"/>
+    <col min="4" max="5" width="46.625" customWidth="1"/>
+    <col min="6" max="7" width="28.625" customWidth="1"/>
+    <col min="8" max="8" width="24.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" ht="27.95" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>142</v>
       </c>
@@ -1803,7 +1860,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
     </row>
-    <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" ht="32.1" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>143</v>
       </c>
@@ -1829,7 +1886,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>150</v>
       </c>
@@ -1855,33 +1912,33 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:8" ht="33.950000000000003" customHeight="1">
+      <c r="A5" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>164</v>
       </c>
@@ -1907,33 +1964,33 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:8" ht="33.950000000000003" customHeight="1">
+      <c r="A7" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="H7" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A8" s="3" t="s">
         <v>174</v>
       </c>
@@ -1959,33 +2016,33 @@
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="3" t="s">
+    <row r="9" spans="1:8" ht="33.950000000000003" customHeight="1">
+      <c r="A9" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="H9" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A10" s="3" t="s">
         <v>185</v>
       </c>
@@ -2012,27 +2069,33 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A3:H10" xr:uid="{F04D56A7-55FA-49B7-A97D-53AA132D8E63}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.3" right="0.3" top="0.44999999999999996" bottom="0.44999999999999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="52" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41CE2A4A-557D-4EB8-8E38-E0EAD1F80082}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE94349D-B647-4883-8B82-0BBD68C6C1F4}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="16.625" customWidth="1"/>
-    <col min="2" max="2" width="24.625" customWidth="1"/>
-    <col min="3" max="3" width="34.625" customWidth="1"/>
-    <col min="4" max="5" width="42.625" customWidth="1"/>
-    <col min="6" max="8" width="28.625" customWidth="1"/>
+    <col min="1" max="1" width="15.625" customWidth="1"/>
+    <col min="2" max="2" width="22.625" customWidth="1"/>
+    <col min="3" max="3" width="36.625" customWidth="1"/>
+    <col min="4" max="5" width="46.625" customWidth="1"/>
+    <col min="6" max="7" width="28.625" customWidth="1"/>
+    <col min="8" max="8" width="24.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" ht="27.95" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>191</v>
       </c>
@@ -2044,7 +2107,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
     </row>
-    <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" ht="32.1" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>69</v>
       </c>
@@ -2070,7 +2133,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>195</v>
       </c>
@@ -2094,31 +2157,31 @@
       </c>
       <c r="H4" s="3"/>
     </row>
-    <row r="5" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:8" ht="33.950000000000003" customHeight="1">
+      <c r="A5" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="H5" s="3"/>
-    </row>
-    <row r="6" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="H5" s="4"/>
+    </row>
+    <row r="6" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>205</v>
       </c>
@@ -2142,35 +2205,37 @@
       </c>
       <c r="H6" s="3"/>
     </row>
-    <row r="7" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:8" ht="33.950000000000003" customHeight="1">
+      <c r="A7" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="H7" s="3"/>
+      <c r="H7" s="4"/>
     </row>
   </sheetData>
+  <autoFilter ref="A3:H7" xr:uid="{DE94349D-B647-4883-8B82-0BBD68C6C1F4}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.3" right="0.3" top="0.44999999999999996" bottom="0.44999999999999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="52" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>